--- a/data/trans_orig/P71_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40256</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50057</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51928</t>
+          <t>52138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84194</t>
+          <t>84168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229903</t>
+          <t>227981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>250832</t>
+          <t>250180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207741</t>
+          <t>205611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231032</t>
+          <t>229875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443763</t>
+          <t>443789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476029</t>
+          <t>475819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101527</t>
+          <t>100358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139406</t>
+          <t>137964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>149090</t>
+          <t>152857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192731</t>
+          <t>193567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264910</t>
+          <t>264482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322232</t>
+          <t>321863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>346841</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>383278</t>
+          <t>384447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297466</t>
+          <t>296630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341107</t>
+          <t>337340</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652770</t>
+          <t>653139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710092</t>
+          <t>710520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>37773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65769</t>
+          <t>65435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70836</t>
+          <t>68267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102111</t>
+          <t>100361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115813</t>
+          <t>116082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158038</t>
+          <t>156334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247488</t>
+          <t>247822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>274370</t>
+          <t>275484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226727</t>
+          <t>228477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258002</t>
+          <t>260571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>484057</t>
+          <t>485761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>526282</t>
+          <t>526013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32515</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56426</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69168</t>
+          <t>70849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102075</t>
+          <t>101680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108277</t>
+          <t>109126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145894</t>
+          <t>148623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300357</t>
+          <t>299954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>324268</t>
+          <t>324698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267846</t>
+          <t>268241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300753</t>
+          <t>299072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>580810</t>
+          <t>578081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>618427</t>
+          <t>617578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>20987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32030</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56896</t>
+          <t>55279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57607</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88460</t>
+          <t>90322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158753</t>
+          <t>159579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179010</t>
+          <t>178795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144326</t>
+          <t>145943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169192</t>
+          <t>169137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312544</t>
+          <t>310682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343397</t>
+          <t>342395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68386</t>
+          <t>68473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73630</t>
+          <t>73533</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103611</t>
+          <t>104936</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122726</t>
+          <t>122616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163691</t>
+          <t>163731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200446</t>
+          <t>200359</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226287</t>
+          <t>227526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170270</t>
+          <t>168945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>200251</t>
+          <t>200348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379023</t>
+          <t>378983</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>419988</t>
+          <t>420098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103114</t>
+          <t>104284</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143373</t>
+          <t>144888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191167</t>
+          <t>191841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241645</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>311090</t>
+          <t>307583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376950</t>
+          <t>370522</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>461142</t>
+          <t>459627</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>501401</t>
+          <t>500231</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>385716</t>
+          <t>385374</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>436194</t>
+          <t>435520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>854926</t>
+          <t>861354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>920786</t>
+          <t>924293</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117064</t>
+          <t>116463</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>158282</t>
+          <t>157906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>171035</t>
+          <t>171523</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221208</t>
+          <t>219214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>296011</t>
+          <t>298475</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>362881</t>
+          <t>362273</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>574414</t>
+          <t>574790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>615632</t>
+          <t>616233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>544542</t>
+          <t>546536</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>594715</t>
+          <t>594227</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1135565</t>
+          <t>1136173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1202435</t>
+          <t>1199971</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>542936</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>626782</t>
+          <t>627470</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>873035</t>
+          <t>873730</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>977713</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1429935</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1569869</t>
+          <t>1577379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2604047</t>
+          <t>2603359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2694424</t>
+          <t>2687893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2337256</t>
+          <t>2336996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2441934</t>
+          <t>2441239</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4975929</t>
+          <t>4968419</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5115863</t>
+          <t>5102619</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99400</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133507</t>
+          <t>134731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95635</t>
+          <t>95930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130422</t>
+          <t>132862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206008</t>
+          <t>206149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254422</t>
+          <t>256520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161231</t>
+          <t>160007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>195338</t>
+          <t>194707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154729</t>
+          <t>152289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189516</t>
+          <t>189221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>325467</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>373881</t>
+          <t>373740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>246292</t>
+          <t>245381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293409</t>
+          <t>292914</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268315</t>
+          <t>267625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>315116</t>
+          <t>315668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>527991</t>
+          <t>528272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>592843</t>
+          <t>596251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208103</t>
+          <t>208598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>255220</t>
+          <t>256131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207540</t>
+          <t>206988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254341</t>
+          <t>255031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431326</t>
+          <t>427918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>496178</t>
+          <t>495897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39419</t>
+          <t>39210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>36418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>61807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81663</t>
+          <t>82687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119593</t>
+          <t>119277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257483</t>
+          <t>257635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283604</t>
+          <t>283813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276393</t>
+          <t>278224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303557</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543461</t>
+          <t>543777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>581391</t>
+          <t>580367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>77770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112688</t>
+          <t>113423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82722</t>
+          <t>84326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116999</t>
+          <t>120671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169628</t>
+          <t>171862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217348</t>
+          <t>221309</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259164</t>
+          <t>258429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294948</t>
+          <t>294082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267201</t>
+          <t>263529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301478</t>
+          <t>299874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>538705</t>
+          <t>534744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>586425</t>
+          <t>584191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>57319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86161</t>
+          <t>86150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65109</t>
+          <t>65252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93855</t>
+          <t>94626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130673</t>
+          <t>131617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169252</t>
+          <t>171372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124498</t>
+          <t>124509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152875</t>
+          <t>153340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125736</t>
+          <t>124965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154482</t>
+          <t>154339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260998</t>
+          <t>258878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299577</t>
+          <t>298633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>32149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55379</t>
+          <t>55852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70236</t>
+          <t>69807</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105700</t>
+          <t>103755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213886</t>
+          <t>214978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239056</t>
+          <t>239276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223596</t>
+          <t>223123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248247</t>
+          <t>246826</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446302</t>
+          <t>448247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481766</t>
+          <t>482195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120971</t>
+          <t>120977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163022</t>
+          <t>162639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>141943</t>
+          <t>141662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188088</t>
+          <t>189482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>272512</t>
+          <t>277856</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>337591</t>
+          <t>341096</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>498431</t>
+          <t>498814</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>540482</t>
+          <t>540476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>505765</t>
+          <t>504371</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>551910</t>
+          <t>552191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1017715</t>
+          <t>1014210</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1082794</t>
+          <t>1077450</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229855</t>
+          <t>228720</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>282502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>254949</t>
+          <t>250142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>310326</t>
+          <t>308052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>495733</t>
+          <t>493159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>571273</t>
+          <t>576500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>490757</t>
+          <t>490378</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>543025</t>
+          <t>544160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>507939</t>
+          <t>510213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>563316</t>
+          <t>568123</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1019872</t>
+          <t>1014645</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1095412</t>
+          <t>1097986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>992066</t>
+          <t>988394</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1098336</t>
+          <t>1099963</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,82 +6815,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1119928</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1059267</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1179250</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2163863</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2087027</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>2239782</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>32,22%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1119928</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1061306</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1178750</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>33,27%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>2163863</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2081858</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>2243353</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2310809</t>
+          <t>2309182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2417079</t>
+          <t>2420751</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,82 +6928,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>67,73%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>71,01%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2422794</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2363472</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2483455</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>68,39%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>70,1%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>4788004</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>4712085</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>4864840</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>67,78%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>70,9%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2253</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>2422794</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>2363972</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2481416</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>68,39%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>66,73%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>4468</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>4788004</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>4708514</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4870009</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>68,87%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90701</t>
+          <t>92234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124652</t>
+          <t>127251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75225</t>
+          <t>74289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106934</t>
+          <t>106659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176592</t>
+          <t>174338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221346</t>
+          <t>220812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168307</t>
+          <t>165708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202258</t>
+          <t>200725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179776</t>
+          <t>180051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>211485</t>
+          <t>212421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>358324</t>
+          <t>358858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>403078</t>
+          <t>405332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177531</t>
+          <t>180416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223644</t>
+          <t>223334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194020</t>
+          <t>194524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241221</t>
+          <t>241230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>388422</t>
+          <t>387837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>451815</t>
+          <t>453557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274367</t>
+          <t>274677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320480</t>
+          <t>317595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279976</t>
+          <t>279967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327177</t>
+          <t>326673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>567393</t>
+          <t>565651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>630786</t>
+          <t>631371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62182</t>
+          <t>62712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92769</t>
+          <t>90871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91212</t>
+          <t>91750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126298</t>
+          <t>125502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163224</t>
+          <t>161981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207412</t>
+          <t>207674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220022</t>
+          <t>221920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250609</t>
+          <t>250079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207563</t>
+          <t>208359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>242649</t>
+          <t>242111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439240</t>
+          <t>438978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>483428</t>
+          <t>484671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94122</t>
+          <t>94714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130518</t>
+          <t>130615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130355</t>
+          <t>129441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167948</t>
+          <t>170726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233324</t>
+          <t>235771</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288019</t>
+          <t>288458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238409</t>
+          <t>238312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274805</t>
+          <t>274213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218411</t>
+          <t>215633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256004</t>
+          <t>256918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>467267</t>
+          <t>466828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>521962</t>
+          <t>519515</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113652</t>
+          <t>113865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142212</t>
+          <t>141262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130149</t>
+          <t>129655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157170</t>
+          <t>156757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252965</t>
+          <t>250540</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291136</t>
+          <t>289931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67042</t>
+          <t>67992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95602</t>
+          <t>95389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60286</t>
+          <t>60699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87307</t>
+          <t>87801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>135574</t>
+          <t>136779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173745</t>
+          <t>176170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37055</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62503</t>
+          <t>62231</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64548</t>
+          <t>65505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81263</t>
+          <t>80475</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116732</t>
+          <t>116059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197640</t>
+          <t>197912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223088</t>
+          <t>224270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>207610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>234934</t>
+          <t>234799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>416526</t>
+          <t>417199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451995</t>
+          <t>452783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>175716</t>
+          <t>175849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>226689</t>
+          <t>224848</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204351</t>
+          <t>204066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>254996</t>
+          <t>252332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394216</t>
+          <t>396011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>465660</t>
+          <t>466243</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>428783</t>
+          <t>430624</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>479756</t>
+          <t>479623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>435329</t>
+          <t>437993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>485974</t>
+          <t>486259</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>880138</t>
+          <t>879555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>951582</t>
+          <t>949787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229365</t>
+          <t>228040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>281964</t>
+          <t>279828</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>239585</t>
+          <t>241758</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>295174</t>
+          <t>294790</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>480242</t>
+          <t>487138</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>561300</t>
+          <t>559754</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>487759</t>
+          <t>489895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>540358</t>
+          <t>541683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>522595</t>
+          <t>522979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>578184</t>
+          <t>576011</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1026193</t>
+          <t>1027739</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1107251</t>
+          <t>1100355</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1075363</t>
+          <t>1069847</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1183427</t>
+          <t>1184093</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1203999</t>
+          <t>1198004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1316227</t>
+          <t>1315886</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2308918</t>
+          <t>2314822</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2472259</t>
+          <t>2470344</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2183855</t>
+          <t>2183189</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2291919</t>
+          <t>2297435</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2210565</t>
+          <t>2210906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2322793</t>
+          <t>2328788</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4421816</t>
+          <t>4423731</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4585157</t>
+          <t>4579253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44040</t>
+          <t>42165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>31590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58347</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285097</t>
+          <t>284537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300409</t>
+          <t>300916</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245595</t>
+          <t>247470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271831</t>
+          <t>272015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541375</t>
+          <t>540687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568166</t>
+          <t>568132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46876</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86922</t>
+          <t>90867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57489</t>
+          <t>57705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85259</t>
+          <t>84990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114271</t>
+          <t>115124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161711</t>
+          <t>161336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423711</t>
+          <t>419766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463757</t>
+          <t>463222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427954</t>
+          <t>428223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455724</t>
+          <t>455508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862135</t>
+          <t>862510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>909575</t>
+          <t>908722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34959</t>
+          <t>35390</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62434</t>
+          <t>63304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>55819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79681</t>
+          <t>80938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98993</t>
+          <t>97642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135613</t>
+          <t>132681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251629</t>
+          <t>250759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279104</t>
+          <t>278673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>264213</t>
+          <t>262956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288784</t>
+          <t>288075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>522344</t>
+          <t>525276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558964</t>
+          <t>560315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21694</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46684</t>
+          <t>45351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81299</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>253604</t>
+          <t>259521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107956</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>341211</t>
+          <t>335175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247343</t>
+          <t>248676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272333</t>
+          <t>273444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177411</t>
+          <t>171494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349716</t>
+          <t>351661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383831</t>
+          <t>389867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617086</t>
+          <t>618044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162733</t>
+          <t>161193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173146</t>
+          <t>172857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>236361</t>
+          <t>235443</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>249404</t>
+          <t>250010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403496</t>
+          <t>403531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420374</t>
+          <t>420488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43355</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>48586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58765</t>
+          <t>58880</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85991</t>
+          <t>84354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226281</t>
+          <t>225018</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246823</t>
+          <t>246398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208392</t>
+          <t>208008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226124</t>
+          <t>226477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>440239</t>
+          <t>441876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467465</t>
+          <t>467350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98261</t>
+          <t>99811</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47795</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126331</t>
+          <t>123600</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102106</t>
+          <t>108519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>202122</t>
+          <t>203279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>515046</t>
+          <t>513496</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>555338</t>
+          <t>553986</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>713681</t>
+          <t>716412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>792217</t>
+          <t>798736</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1251197</t>
+          <t>1250040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351213</t>
+          <t>1344800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>66901</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194011</t>
+          <t>196164</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140436</t>
+          <t>140258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>182445</t>
+          <t>181461</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>185621</t>
+          <t>175220</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>360613</t>
+          <t>359496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>731930</t>
+          <t>729777</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>863108</t>
+          <t>859040</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>530602</t>
+          <t>531586</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>572611</t>
+          <t>572789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1278375</t>
+          <t>1279492</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1453367</t>
+          <t>1463768</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>329674</t>
+          <t>317457</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>465813</t>
+          <t>466090</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>518264</t>
+          <t>504971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>809900</t>
+          <t>788405</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>904865</t>
+          <t>894116</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1231268</t>
+          <t>1219741</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2950090</t>
+          <t>2949813</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3086229</t>
+          <t>3098446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2833822</t>
+          <t>2855317</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3125458</t>
+          <t>3138751</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5828357</t>
+          <t>5839884</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6154760</t>
+          <t>6165509</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P71_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>40993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>27517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52138</t>
+          <t>53614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84168</t>
+          <t>85921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227981</t>
+          <t>229166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>250180</t>
+          <t>250125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205611</t>
+          <t>206345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229875</t>
+          <t>230281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443789</t>
+          <t>442036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475819</t>
+          <t>474343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100358</t>
+          <t>101983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137964</t>
+          <t>139893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152857</t>
+          <t>153076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>193567</t>
+          <t>194223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264482</t>
+          <t>262401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321863</t>
+          <t>320207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346841</t>
+          <t>344912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>384447</t>
+          <t>382822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296630</t>
+          <t>295974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337340</t>
+          <t>337121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>653139</t>
+          <t>654795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710520</t>
+          <t>712601</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65435</t>
+          <t>65159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,47 +1434,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>83966</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98589</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>20,89%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>83966</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>68267</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>100361</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,53%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116082</t>
+          <t>116309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156334</t>
+          <t>156183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247822</t>
+          <t>248098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275484</t>
+          <t>274735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,49 +1547,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>79,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>244872</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>230249</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>260140</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>74,47%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>70,02%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>79,11%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>244872</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>228477</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>260571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,47%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>69,48%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>79,24%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>503</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>485761</t>
+          <t>485912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>526013</t>
+          <t>525786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56829</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70849</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101680</t>
+          <t>101323</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109126</t>
+          <t>108277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148623</t>
+          <t>149367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>299954</t>
+          <t>300795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>324698</t>
+          <t>325978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>268241</t>
+          <t>268598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299072</t>
+          <t>300187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>578081</t>
+          <t>577337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617578</t>
+          <t>618427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40203</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>32108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55279</t>
+          <t>55968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>57767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90322</t>
+          <t>88227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159579</t>
+          <t>159506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178795</t>
+          <t>178718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145943</t>
+          <t>145254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169137</t>
+          <t>169114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310682</t>
+          <t>312777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342395</t>
+          <t>343237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>43010</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68473</t>
+          <t>70624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73533</t>
+          <t>72980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104936</t>
+          <t>103353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122616</t>
+          <t>123065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163731</t>
+          <t>163559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200359</t>
+          <t>198208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227526</t>
+          <t>225822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168945</t>
+          <t>170528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>200348</t>
+          <t>200901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>378983</t>
+          <t>379155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420098</t>
+          <t>419649</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104284</t>
+          <t>102939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144888</t>
+          <t>142750</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191841</t>
+          <t>194792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>242079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>307583</t>
+          <t>309063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370522</t>
+          <t>373532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>459627</t>
+          <t>461765</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>500231</t>
+          <t>501576</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>385374</t>
+          <t>385282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>435520</t>
+          <t>432569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>861354</t>
+          <t>858344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>924293</t>
+          <t>922813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116463</t>
+          <t>113547</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>156576</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>171523</t>
+          <t>172900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219214</t>
+          <t>222497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>298475</t>
+          <t>299046</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>362273</t>
+          <t>364524</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>574790</t>
+          <t>576120</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>616233</t>
+          <t>619149</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>546536</t>
+          <t>543253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>594227</t>
+          <t>592850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1136173</t>
+          <t>1133922</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1199971</t>
+          <t>1199400</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>542936</t>
+          <t>539752</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>627470</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>873730</t>
+          <t>872523</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>977973</t>
+          <t>974556</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1443179</t>
+          <t>1440326</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1577379</t>
+          <t>1578494</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2603359</t>
+          <t>2602688</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2687893</t>
+          <t>2691077</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2336996</t>
+          <t>2340413</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2441239</t>
+          <t>2442446</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4968419</t>
+          <t>4967304</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5102619</t>
+          <t>5105472</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100031</t>
+          <t>99927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134731</t>
+          <t>134299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95930</t>
+          <t>95762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132862</t>
+          <t>131103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206149</t>
+          <t>206465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256520</t>
+          <t>254915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160007</t>
+          <t>160439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194707</t>
+          <t>194811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152289</t>
+          <t>154048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189221</t>
+          <t>189389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>323369</t>
+          <t>324974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>373740</t>
+          <t>373424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>245381</t>
+          <t>245691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>292914</t>
+          <t>291388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>267625</t>
+          <t>268346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>315668</t>
+          <t>316164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>528272</t>
+          <t>526066</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>596251</t>
+          <t>594905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208598</t>
+          <t>210124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>256131</t>
+          <t>255821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206988</t>
+          <t>206492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>255031</t>
+          <t>254310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427918</t>
+          <t>429264</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495897</t>
+          <t>498103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39210</t>
+          <t>39242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65388</t>
+          <t>67075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61807</t>
+          <t>62983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82687</t>
+          <t>83546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119277</t>
+          <t>119997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257635</t>
+          <t>255948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283813</t>
+          <t>283781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278224</t>
+          <t>277048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>303706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543777</t>
+          <t>543057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>580367</t>
+          <t>579508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>78564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113423</t>
+          <t>113806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84326</t>
+          <t>82676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120671</t>
+          <t>116593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171862</t>
+          <t>171351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221309</t>
+          <t>221507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258429</t>
+          <t>258046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294082</t>
+          <t>293288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263529</t>
+          <t>267607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299874</t>
+          <t>301524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>534744</t>
+          <t>534546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>584191</t>
+          <t>584702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57319</t>
+          <t>57853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86150</t>
+          <t>87002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65252</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94626</t>
+          <t>94338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131617</t>
+          <t>130723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171372</t>
+          <t>171474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124509</t>
+          <t>123657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153340</t>
+          <t>152806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124965</t>
+          <t>125253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154339</t>
+          <t>154388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258878</t>
+          <t>258776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298633</t>
+          <t>299527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33751</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32149</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55852</t>
+          <t>57406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69807</t>
+          <t>72037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103755</t>
+          <t>107298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214978</t>
+          <t>214819</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239276</t>
+          <t>239479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223123</t>
+          <t>221569</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246826</t>
+          <t>247817</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>448247</t>
+          <t>444704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482195</t>
+          <t>479965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120977</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162639</t>
+          <t>164635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>141662</t>
+          <t>143413</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189482</t>
+          <t>189208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277856</t>
+          <t>273788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>341096</t>
+          <t>339002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>498814</t>
+          <t>496818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>540476</t>
+          <t>542169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>504371</t>
+          <t>504645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>552191</t>
+          <t>550440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1014210</t>
+          <t>1016304</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1077450</t>
+          <t>1081518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>228720</t>
+          <t>227754</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>282502</t>
+          <t>282617</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250142</t>
+          <t>252774</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>308052</t>
+          <t>307811</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>493159</t>
+          <t>494435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>576500</t>
+          <t>571601</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>490378</t>
+          <t>490263</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>544160</t>
+          <t>545126</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>510213</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>568123</t>
+          <t>565491</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1014645</t>
+          <t>1019544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1097986</t>
+          <t>1096710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>988394</t>
+          <t>989070</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1099963</t>
+          <t>1096750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1059267</t>
+          <t>1061488</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1179250</t>
+          <t>1178397</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2087027</t>
+          <t>2084308</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2239782</t>
+          <t>2246181</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2309182</t>
+          <t>2312395</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2420751</t>
+          <t>2420075</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2363472</t>
+          <t>2364325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2483455</t>
+          <t>2481234</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4712085</t>
+          <t>4705686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4864840</t>
+          <t>4867559</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92234</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127251</t>
+          <t>126308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74289</t>
+          <t>75430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106659</t>
+          <t>107147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174338</t>
+          <t>174568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220812</t>
+          <t>223564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165708</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200725</t>
+          <t>201754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180051</t>
+          <t>179563</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212421</t>
+          <t>211280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>358858</t>
+          <t>356106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405332</t>
+          <t>405102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180416</t>
+          <t>179803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223334</t>
+          <t>224833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>195993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241230</t>
+          <t>241314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387837</t>
+          <t>384394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453557</t>
+          <t>451880</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274677</t>
+          <t>273178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317595</t>
+          <t>318208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279967</t>
+          <t>279883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326673</t>
+          <t>325204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565651</t>
+          <t>567328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>631371</t>
+          <t>634814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62712</t>
+          <t>62584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>91331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91750</t>
+          <t>92554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125502</t>
+          <t>127178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161981</t>
+          <t>163511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207674</t>
+          <t>208098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221920</t>
+          <t>221460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250079</t>
+          <t>250207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>208359</t>
+          <t>206683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>242111</t>
+          <t>241307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>438978</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>484671</t>
+          <t>483141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94714</t>
+          <t>94441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130615</t>
+          <t>130966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129441</t>
+          <t>127518</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170726</t>
+          <t>168600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235771</t>
+          <t>233482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288458</t>
+          <t>287884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238312</t>
+          <t>237961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274213</t>
+          <t>274486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>215633</t>
+          <t>217759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256918</t>
+          <t>258841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>466828</t>
+          <t>467402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519515</t>
+          <t>521804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113865</t>
+          <t>113806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141262</t>
+          <t>142890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129655</t>
+          <t>130856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>156757</t>
+          <t>158122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250540</t>
+          <t>253826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289931</t>
+          <t>292959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67992</t>
+          <t>66364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95389</t>
+          <t>95448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60699</t>
+          <t>59334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87801</t>
+          <t>86600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136779</t>
+          <t>133751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176170</t>
+          <t>172884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38316</t>
+          <t>38647</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>64128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80475</t>
+          <t>80907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116059</t>
+          <t>118071</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197912</t>
+          <t>198204</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224270</t>
+          <t>225063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207610</t>
+          <t>208987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>234799</t>
+          <t>234468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>417199</t>
+          <t>415187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>452783</t>
+          <t>452351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>175849</t>
+          <t>176422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224848</t>
+          <t>225503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204066</t>
+          <t>206840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252332</t>
+          <t>257454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396011</t>
+          <t>394838</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>466243</t>
+          <t>465411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>430624</t>
+          <t>429969</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>479623</t>
+          <t>479050</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>437993</t>
+          <t>432871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>486259</t>
+          <t>483485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>879555</t>
+          <t>880387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>949787</t>
+          <t>950960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,66%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>228040</t>
+          <t>227837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>279828</t>
+          <t>281709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>241758</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>294790</t>
+          <t>294897</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>487138</t>
+          <t>486172</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>559754</t>
+          <t>563911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>489895</t>
+          <t>488014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>541683</t>
+          <t>541886</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>522979</t>
+          <t>522872</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>576011</t>
+          <t>576652</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1027739</t>
+          <t>1023582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1100355</t>
+          <t>1101321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1069847</t>
+          <t>1072306</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1184093</t>
+          <t>1181665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1198004</t>
+          <t>1201964</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1315886</t>
+          <t>1319856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2314822</t>
+          <t>2305668</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2470344</t>
+          <t>2468465</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2183189</t>
+          <t>2185617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2297435</t>
+          <t>2294976</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2210906</t>
+          <t>2206936</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2328788</t>
+          <t>2324828</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4423731</t>
+          <t>4425610</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4579253</t>
+          <t>4588407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17620</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42165</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31590</t>
+          <t>42912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>294435</t>
+          <t>293886</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284537</t>
+          <t>284452</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300916</t>
+          <t>302247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>262800</t>
+          <t>285806</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247470</t>
+          <t>273143</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272015</t>
+          <t>293581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>557235</t>
+          <t>579692</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540687</t>
+          <t>562700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568132</t>
+          <t>590801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>310087</t>
+          <t>317652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310087</t>
+          <t>317652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310087</t>
+          <t>317652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>599722</t>
+          <t>633713</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>599722</t>
+          <t>633713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>599722</t>
+          <t>633713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47411</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90867</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70402</t>
+          <t>76139</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>61955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84990</t>
+          <t>92337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>136310</t>
+          <t>143389</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115124</t>
+          <t>121864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161336</t>
+          <t>167117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>444725</t>
+          <t>456255</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>419766</t>
+          <t>435874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463222</t>
+          <t>473403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442811</t>
+          <t>468522</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428223</t>
+          <t>452324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455508</t>
+          <t>482706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>887536</t>
+          <t>924777</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862510</t>
+          <t>901049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908722</t>
+          <t>946302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>523505</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>523505</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>523505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513213</t>
+          <t>544661</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513213</t>
+          <t>544661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513213</t>
+          <t>544661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1023846</t>
+          <t>1068166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1023846</t>
+          <t>1068166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1023846</t>
+          <t>1068166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>39164</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63304</t>
+          <t>64508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>67289</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55819</t>
+          <t>58787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80938</t>
+          <t>85061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>114555</t>
+          <t>122721</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97642</t>
+          <t>105702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132681</t>
+          <t>141629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>266797</t>
+          <t>261640</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250759</t>
+          <t>248069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278673</t>
+          <t>273413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>276605</t>
+          <t>279423</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>262956</t>
+          <t>266146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288075</t>
+          <t>292420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>543402</t>
+          <t>541063</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525276</t>
+          <t>522155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>560315</t>
+          <t>558082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314063</t>
+          <t>312577</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314063</t>
+          <t>312577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314063</t>
+          <t>312577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>343894</t>
+          <t>351207</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>343894</t>
+          <t>351207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>343894</t>
+          <t>351207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>657957</t>
+          <t>663784</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>657957</t>
+          <t>663784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>657957</t>
+          <t>663784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20583</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>141495</t>
+          <t>83553</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>67833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259521</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>172859</t>
+          <t>131877</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106998</t>
+          <t>109732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335175</t>
+          <t>156999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262664</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248676</t>
+          <t>283302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273444</t>
+          <t>319032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>289520</t>
+          <t>324772</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171494</t>
+          <t>308197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351661</t>
+          <t>340492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>552183</t>
+          <t>628517</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>389867</t>
+          <t>603395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>618044</t>
+          <t>650662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>294027</t>
+          <t>352069</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>294027</t>
+          <t>352069</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>294027</t>
+          <t>352069</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>431015</t>
+          <t>408325</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>431015</t>
+          <t>408325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>431015</t>
+          <t>408325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>725042</t>
+          <t>760394</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>725042</t>
+          <t>760394</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>725042</t>
+          <t>760394</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>23581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>31563</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>169147</t>
+          <t>189856</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161193</t>
+          <t>181513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172857</t>
+          <t>196234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>243372</t>
+          <t>209890</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235443</t>
+          <t>202097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250010</t>
+          <t>215438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>412519</t>
+          <t>399746</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403531</t>
+          <t>388938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420488</t>
+          <t>407730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178208</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178208</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178208</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>256313</t>
+          <t>226215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>256313</t>
+          <t>226215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256313</t>
+          <t>226215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>434521</t>
+          <t>431309</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>434521</t>
+          <t>431309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>434521</t>
+          <t>431309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30117</t>
+          <t>33744</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48586</t>
+          <t>52723</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>78946</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58880</t>
+          <t>66517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>237544</t>
+          <t>234019</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225018</t>
+          <t>222310</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246398</t>
+          <t>243217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>217553</t>
+          <t>221011</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208008</t>
+          <t>210546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226477</t>
+          <t>229525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>455097</t>
+          <t>455030</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>441876</t>
+          <t>441080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467350</t>
+          <t>467459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256594</t>
+          <t>263269</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256594</t>
+          <t>263269</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256594</t>
+          <t>263269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526230</t>
+          <t>533976</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526230</t>
+          <t>533976</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526230</t>
+          <t>533976</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>75852</t>
+          <t>85240</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59321</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99811</t>
+          <t>106394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>111544</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>93980</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123600</t>
+          <t>129710</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>165682</t>
+          <t>196784</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108519</t>
+          <t>171973</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203279</t>
+          <t>225641</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>537455</t>
+          <t>619478</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>513496</t>
+          <t>598324</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>553986</t>
+          <t>637451</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>750182</t>
+          <t>648924</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>716412</t>
+          <t>630758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>798736</t>
+          <t>666488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1287637</t>
+          <t>1268402</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1250040</t>
+          <t>1239545</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344800</t>
+          <t>1293213</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>613307</t>
+          <t>704718</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>613307</t>
+          <t>704718</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>613307</t>
+          <t>704718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>840012</t>
+          <t>760468</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>840012</t>
+          <t>760468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>840012</t>
+          <t>760468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1453319</t>
+          <t>1465186</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1453319</t>
+          <t>1465186</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1453319</t>
+          <t>1465186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>137204</t>
+          <t>171296</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66901</t>
+          <t>148337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196164</t>
+          <t>198036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>159735</t>
+          <t>191722</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140258</t>
+          <t>170788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181461</t>
+          <t>213852</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>296939</t>
+          <t>363018</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175220</t>
+          <t>329243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>359496</t>
+          <t>398323</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>788737</t>
+          <t>623667</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729777</t>
+          <t>596927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>859040</t>
+          <t>646626</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>553312</t>
+          <t>635488</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>531586</t>
+          <t>613358</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>572789</t>
+          <t>656422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1342049</t>
+          <t>1259155</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1279492</t>
+          <t>1223850</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1463768</t>
+          <t>1292930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925941</t>
+          <t>794963</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925941</t>
+          <t>794963</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925941</t>
+          <t>794963</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>713047</t>
+          <t>827210</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>713047</t>
+          <t>827210</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>713047</t>
+          <t>827210</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1638988</t>
+          <t>1622173</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1638988</t>
+          <t>1622173</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1638988</t>
+          <t>1622173</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>317457</t>
+          <t>452722</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>466090</t>
+          <t>545741</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>504971</t>
+          <t>581647</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>788405</t>
+          <t>665420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>894116</t>
+          <t>1057634</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1219741</t>
+          <t>1186356</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3001505</t>
+          <t>2982545</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2949813</t>
+          <t>2935543</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3098446</t>
+          <t>3028562</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3036154</t>
+          <t>3073836</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2855317</t>
+          <t>3031996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3138751</t>
+          <t>3115769</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6037659</t>
+          <t>6056381</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5839884</t>
+          <t>5992345</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6165509</t>
+          <t>6121067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
